--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2021_metropolitana.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2021_metropolitana.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:29</t>
+    <t xml:space="preserve">2026-09-24 01:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -789,7 +789,7 @@
         <v>0.16</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="12">
@@ -829,13 +829,13 @@
         <v>21</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="14">
@@ -1220,13 +1220,13 @@
         <v>21</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="31">
@@ -1571,7 +1571,7 @@
         <v>0.21</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="46">
@@ -1611,10 +1611,10 @@
         <v>21</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>-0.28</v>
@@ -2002,13 +2002,13 @@
         <v>21</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.2</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>0.07</v>
+        <v>0.08</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="65">
@@ -2327,10 +2327,10 @@
         <v>0.39</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>0.19</v>
+        <v>0.28</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.2</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="79">
@@ -2350,10 +2350,10 @@
         <v>0.17</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>-0.02</v>
+        <v>0.15</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>0.19</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="80">
@@ -2373,10 +2373,10 @@
         <v>0.3</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.1</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="81">
@@ -2393,13 +2393,13 @@
         <v>21</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="82">
@@ -2442,10 +2442,10 @@
         <v>-0.5</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>-0.13</v>
+        <v>0.72</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>-0.38</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="84">
@@ -2465,10 +2465,10 @@
         <v>-0.27</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.7</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>-0.08</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="85">
@@ -2488,10 +2488,10 @@
         <v>-0.54</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.1</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>-0.37</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="86">
@@ -2718,10 +2718,10 @@
         <v>0.37</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>-0.09</v>
+        <v>0.06</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>0.45</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="96">
@@ -2741,10 +2741,10 @@
         <v>0.38</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>0.03</v>
+        <v>0.14</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.35</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="97">
@@ -2764,10 +2764,10 @@
         <v>0.14</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>0.23</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="98">
@@ -2787,10 +2787,10 @@
         <v>-0.21</v>
       </c>
       <c r="F98" s="2" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="G98" s="2" t="n">
         <v>-0.13</v>
-      </c>
-      <c r="G98" s="2" t="n">
-        <v>-0.08</v>
       </c>
     </row>
     <row r="99">
@@ -2833,10 +2833,10 @@
         <v>-0.07</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>0.1</v>
+        <v>0.58</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="101">
@@ -2856,10 +2856,10 @@
         <v>-0.5</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>0</v>
+        <v>-0.46</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>-0.5</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="102">
@@ -2882,7 +2882,7 @@
         <v>-0.03</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="103">
@@ -3109,10 +3109,10 @@
         <v>0.02</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.05</v>
       </c>
       <c r="G112" s="2" t="n">
-        <v>0.14</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="113">
@@ -3132,10 +3132,10 @@
         <v>-0.21</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.19</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.07</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="114">
@@ -3155,10 +3155,10 @@
         <v>0.14</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="115">
@@ -3175,10 +3175,10 @@
         <v>21</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="G115" s="2" t="n">
         <v>0.14</v>
@@ -3224,10 +3224,10 @@
         <v>-0.33</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>-0.22</v>
+        <v>0.2</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="118">
@@ -3247,10 +3247,10 @@
         <v>-0.01</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>0.01</v>
+        <v>-0.24</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>-0.02</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="119">
@@ -3500,10 +3500,10 @@
         <v>-0.28</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.33</v>
       </c>
       <c r="G129" s="2" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="130">
@@ -3523,10 +3523,10 @@
         <v>-0.52</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.26</v>
       </c>
       <c r="G130" s="2" t="n">
-        <v>-0.35</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="131">
@@ -3566,13 +3566,13 @@
         <v>21</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="133">
@@ -3615,10 +3615,10 @@
         <v>-0.07</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.84</v>
       </c>
       <c r="G134" s="2" t="n">
-        <v>0.08</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="135">
@@ -3638,10 +3638,10 @@
         <v>0.31</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>0.05</v>
+        <v>0.72</v>
       </c>
       <c r="G135" s="2" t="n">
-        <v>0.26</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="136">
@@ -3661,10 +3661,10 @@
         <v>0.11</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G136" s="2" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="137">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2021_metropolitana.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2021_metropolitana.xlsx
@@ -102,7 +102,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:19</t>
+    <t xml:space="preserve">2026-10-01 23:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2021_metropolitana.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2021_metropolitana.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:19</t>
+    <t xml:space="preserve">2026-10-05 19:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
